--- a/output/2026-09-05_10_Italia_Calabria_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-05_10_Italia_Calabria_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -472,7 +472,6 @@
           <t>Gimal S.r.l.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Reggio Calabria (RC)</t>
@@ -490,7 +489,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Distributore all'ingrosso di macchine/utensili per lavorazione legno e metalli, impianti di aspirazione, cabine di verniciatura, aria compressa. Confermato su piu' fonti indipendenti (europages, paginebianche, kompass, paginegialle, reteimprese).</t>
+          <t>Distributore all'ingrosso di macchine/utensili per lavorazione legno e metalli, impianti di aspirazione, cabine di verniciatura, aria compressa. Confermato su piu' fonti indipendenti (europages, paginebianche, kompass, paginegialle, reteimprese). [DUPLICATO — vedi anche: 2026-09-05_00_Italia_Calabria_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -527,7 +526,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Distribuzione/assemblaggio/manutenzione impianti e attrezzature per officine meccaniche, elettrauto, gommisti, carrozzieri; ATECO 46.62 commercio ingrosso macchine utensili confermato. Focus settoriale misto (automotive/gommisti prevalente) - incluso con riserva.</t>
+          <t>Distribuzione/assemblaggio/manutenzione impianti e attrezzature per officine meccaniche, elettrauto, gommisti, carrozzieri; ATECO 46.62 commercio ingrosso macchine utensili confermato. Focus settoriale misto (automotive/gommisti prevalente) - incluso con riserva. [DUPLICATO — vedi anche: 2026-09-05_00_Italia_Calabria_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -542,7 +541,6 @@
           <t>Piro Mario</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Cosenza (CS)</t>
@@ -590,7 +588,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Agenzia di rappresentanza e vendita macchine utensili per lavorazione lamiera (presse piegatrici CNC, cesoie, taglio plasma/laser, punzonatrici). Esistenza confermata via ricerca incrociata; indirizzo/telefono/email non reperiti con certezza (WebFetch fallito per errore di rete). Non confondere con 'arcom.it' di Brescia (azienda diversa e non correlata).</t>

--- a/output/2026-09-05_10_Italia_Calabria_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-05_10_Italia_Calabria_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
